--- a/public/tableau-synthese-bts-adrien-clavreul.xlsx
+++ b/public/tableau-synthese-bts-adrien-clavreul.xlsx
@@ -46,7 +46,7 @@
     <t>✓ SLAM</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio : https://adrien-clavreul.fr</t>
+    <t>Adresse URL du portfolio : https://adrien-cl.github.io/portfolio/</t>
   </si>
   <si>
     <t xml:space="preserve">Compétences mises en œuvre
